--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>13</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>18</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>6</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>19</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>11</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>12</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>12</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>12</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>9</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>7</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>6</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>8</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>5</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>7</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>7</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>33</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>19</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>8</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>10</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>6</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>6</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>4</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>19</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>8</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>9</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>8</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>7</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>14</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>4</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>13</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>4</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>4</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>6</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>17</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>6</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>9</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>8</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>12</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20167,9 +20020,6 @@
       <c r="O101" t="n">
         <v>20</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20560,9 +20410,6 @@
       <c r="O103" t="n">
         <v>15</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20953,9 +20800,6 @@
       <c r="O105" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21491,9 +21335,6 @@
       <c r="O108" t="n">
         <v>17</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21884,9 +21725,6 @@
       <c r="O110" t="n">
         <v>6</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22422,9 +22260,6 @@
       <c r="O113" t="n">
         <v>8</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22815,9 +22650,6 @@
       <c r="O115" t="n">
         <v>5</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23353,9 +23185,6 @@
       <c r="O118" t="n">
         <v>14</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23746,9 +23575,6 @@
       <c r="O120" t="n">
         <v>5</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24284,9 +24110,6 @@
       <c r="O123" t="n">
         <v>8</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24677,9 +24500,6 @@
       <c r="O125" t="n">
         <v>2</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25215,9 +25035,6 @@
       <c r="O128" t="n">
         <v>7</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25608,9 +25425,6 @@
       <c r="O130" t="n">
         <v>4</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26146,9 +25960,6 @@
       <c r="O133" t="n">
         <v>11</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26539,9 +26350,6 @@
       <c r="O135" t="n">
         <v>7</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27077,9 +26885,6 @@
       <c r="O138" t="n">
         <v>8</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27470,9 +27275,6 @@
       <c r="O140" t="n">
         <v>3</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28008,9 +27810,6 @@
       <c r="O143" t="n">
         <v>5</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28401,9 +28200,6 @@
       <c r="O145" t="n">
         <v>3</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28939,9 +28735,6 @@
       <c r="O148" t="n">
         <v>9</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29332,9 +29125,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29870,9 +29660,6 @@
       <c r="O153" t="n">
         <v>5</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30263,9 +30050,6 @@
       <c r="O155" t="n">
         <v>3</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30801,9 +30585,6 @@
       <c r="O158" t="n">
         <v>8</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31194,9 +30975,6 @@
       <c r="O160" t="n">
         <v>10</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31732,9 +31510,6 @@
       <c r="O163" t="n">
         <v>16</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32125,9 +31900,6 @@
       <c r="O165" t="n">
         <v>6</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32518,9 +32290,6 @@
       <c r="O167" t="n">
         <v>2</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33056,9 +32825,6 @@
       <c r="O170" t="n">
         <v>9</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33449,9 +33215,6 @@
       <c r="O172" t="n">
         <v>8</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33987,9 +33750,6 @@
       <c r="O175" t="n">
         <v>14</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34380,9 +34140,6 @@
       <c r="O177" t="n">
         <v>4</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34918,9 +34675,6 @@
       <c r="O180" t="n">
         <v>11</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35311,9 +35065,6 @@
       <c r="O182" t="n">
         <v>4</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35849,9 +35600,6 @@
       <c r="O185" t="n">
         <v>11</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36242,9 +35990,6 @@
       <c r="O187" t="n">
         <v>1</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36780,9 +36525,6 @@
       <c r="O190" t="n">
         <v>6</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37173,9 +36915,6 @@
       <c r="O192" t="n">
         <v>4</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37711,9 +37450,6 @@
       <c r="O195" t="n">
         <v>9</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38104,9 +37840,6 @@
       <c r="O197" t="n">
         <v>1</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38642,9 +38375,6 @@
       <c r="O200" t="n">
         <v>5</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39035,9 +38765,6 @@
       <c r="O202" t="n">
         <v>5</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39573,9 +39300,6 @@
       <c r="O205" t="n">
         <v>7</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39966,9 +39690,6 @@
       <c r="O207" t="n">
         <v>3</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40504,9 +40225,6 @@
       <c r="O210" t="n">
         <v>11</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40897,9 +40615,6 @@
       <c r="O212" t="n">
         <v>5</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41435,9 +41150,6 @@
       <c r="O215" t="n">
         <v>4</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41828,9 +41540,6 @@
       <c r="O217" t="n">
         <v>5</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42366,9 +42075,6 @@
       <c r="O220" t="n">
         <v>12</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42759,9 +42465,6 @@
       <c r="O222" t="n">
         <v>6</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43297,9 +43000,6 @@
       <c r="O225" t="n">
         <v>21</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43690,9 +43390,6 @@
       <c r="O227" t="n">
         <v>6</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44083,9 +43780,6 @@
       <c r="O229" t="n">
         <v>9</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44621,9 +44315,6 @@
       <c r="O232" t="n">
         <v>10</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45014,9 +44705,6 @@
       <c r="O234" t="n">
         <v>5</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45552,9 +45240,6 @@
       <c r="O237" t="n">
         <v>13</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45945,9 +45630,6 @@
       <c r="O239" t="n">
         <v>3</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46483,9 +46165,6 @@
       <c r="O242" t="n">
         <v>3</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46876,9 +46555,6 @@
       <c r="O244" t="n">
         <v>7</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47414,9 +47090,6 @@
       <c r="O247" t="n">
         <v>7</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47807,9 +47480,6 @@
       <c r="O249" t="n">
         <v>8</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48345,9 +48015,6 @@
       <c r="O252" t="n">
         <v>4</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48738,9 +48405,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49276,9 +48940,6 @@
       <c r="O257" t="n">
         <v>5</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49669,9 +49330,6 @@
       <c r="O259" t="n">
         <v>5</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50207,9 +49865,6 @@
       <c r="O262" t="n">
         <v>6</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50600,9 +50255,6 @@
       <c r="O264" t="n">
         <v>2</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51138,9 +50790,6 @@
       <c r="O267" t="n">
         <v>8</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51531,9 +51180,6 @@
       <c r="O269" t="n">
         <v>2</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52069,9 +51715,6 @@
       <c r="O272" t="n">
         <v>5</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52462,9 +52105,6 @@
       <c r="O274" t="n">
         <v>5</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53000,9 +52640,6 @@
       <c r="O277" t="n">
         <v>8</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="S277" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53393,9 +53030,6 @@
       <c r="O279" t="n">
         <v>2</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53930,9 +53564,6 @@
       </c>
       <c r="O282" t="n">
         <v>8</v>
-      </c>
-      <c r="Q282" t="n">
-        <v>0</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>

--- a/diseases/d110/1995-1999.xlsx
+++ b/diseases/d110/1995-1999.xlsx
@@ -42421,12 +42421,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -42460,10 +42460,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O222" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -42472,12 +42472,12 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CZ_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -42492,12 +42492,12 @@
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CZ_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -42505,47 +42505,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -42577,12 +42577,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -42616,29 +42616,29 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O223" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CZ_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CZ_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CZ_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>Meningococcus, total</t>
+          <t>Invasive meningococcal disease</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -42648,12 +42648,12 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
@@ -42663,7 +42663,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CZ:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -42698,17 +42698,17 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -42726,12 +42726,12 @@
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_CZ_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -42739,47 +42739,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -42811,12 +42811,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -42850,10 +42850,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>411</v>
+        <v>947</v>
       </c>
       <c r="O224" t="n">
-        <v>411</v>
+        <v>947</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -42887,7 +42887,7 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -42905,7 +42905,7 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
@@ -42925,7 +42925,7 @@
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
@@ -42967,12 +42967,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -43006,24 +43006,24 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>411</v>
+        <v>947</v>
       </c>
       <c r="O225" t="n">
-        <v>411</v>
+        <v>947</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
+          <t>SRC_ES_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
@@ -43053,7 +43053,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>country:FR:national</t>
+          <t>country:ES:national</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -43093,7 +43093,7 @@
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -43121,7 +43121,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+          <t>SER_ES_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -43139,7 +43139,7 @@
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
@@ -43159,7 +43159,7 @@
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
@@ -43201,12 +43201,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -43240,81 +43240,92 @@
         </is>
       </c>
       <c r="N226" t="n">
+        <v>6</v>
+      </c>
+      <c r="O226" t="n">
+        <v>6</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
         <v>1</v>
       </c>
-      <c r="O226" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP226" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
-      <c r="AT226" t="n">
-        <v>0</v>
-      </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43341,17 +43352,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -43385,25 +43396,103 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O227" t="n">
-        <v>21</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -43417,12 +43506,12 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -43430,47 +43519,47 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43497,17 +43586,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -43541,39 +43630,19 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="O228" t="n">
-        <v>21</v>
+        <v>411</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Meningókokkasjúkdómur</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_FR_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -43581,64 +43650,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
-      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43656,7 +43667,7 @@
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+          <t>SER_FR_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -43669,42 +43680,42 @@
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -43731,17 +43742,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -43775,25 +43786,103 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>6</v>
+        <v>411</v>
       </c>
       <c r="O229" t="n">
-        <v>6</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>411</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Invasive meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -43812,7 +43901,7 @@
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FR_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -43825,42 +43914,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -43887,17 +43976,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -43931,103 +44020,25 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="O230" t="n">
-        <v>6</v>
+        <v>193</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_GR_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
+          <t>annual</t>
+        </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -44046,7 +44057,7 @@
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_GR_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT230" t="n">
@@ -44059,42 +44070,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -44121,17 +44132,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -44156,34 +44167,112 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N231" t="n">
-        <v>9</v>
+        <v>193</v>
       </c>
       <c r="O231" t="n">
-        <v>9</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>193</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_GR_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Invasive meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
@@ -44197,12 +44286,12 @@
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_GR_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT231" t="n">
@@ -44210,47 +44299,47 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -44277,17 +44366,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -44312,179 +44401,90 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>9</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
         <v>1</v>
       </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44516,12 +44516,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -44546,90 +44546,101 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -44656,17 +44667,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -44691,34 +44702,112 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N234" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O234" t="n">
-        <v>10</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>21</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Meningókokkasjúkdómur</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
@@ -44737,7 +44826,7 @@
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_IS_HISTORY_MENINGOCOCCAL_ANNUAL</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -44750,42 +44839,42 @@
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -44812,17 +44901,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44847,112 +44936,34 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>10</v>
+        <v>254</v>
       </c>
       <c r="O235" t="n">
-        <v>10</v>
+        <v>254</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_IT_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
+          <t>annual</t>
+        </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -44971,7 +44982,7 @@
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_IT_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT235" t="n">
@@ -44984,42 +44995,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -45046,17 +45057,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -45081,34 +45092,112 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>5</v>
+        <v>254</v>
       </c>
       <c r="O236" t="n">
-        <v>5</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>254</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_IT_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_IT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Invasive meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:IT:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
@@ -45122,12 +45211,12 @@
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_IT_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT236" t="n">
@@ -45135,47 +45224,47 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -45202,17 +45291,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -45237,48 +45326,28 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N237" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O237" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W237" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -45286,64 +45355,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE237" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG237" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK237" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM237" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN237" t="b">
-        <v>1</v>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45356,12 +45367,12 @@
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT237" t="n">
@@ -45369,47 +45380,47 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45436,17 +45447,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -45471,90 +45482,179 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45586,12 +45686,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -45616,19 +45716,19 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N239" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="O239" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -45637,12 +45737,12 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_PL_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -45662,7 +45762,7 @@
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_PL_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT239" t="n">
@@ -45675,42 +45775,42 @@
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -45742,12 +45842,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -45772,38 +45872,38 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="O240" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_PL_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_PL_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_PL_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>Syst. meningokokksykdom</t>
+          <t>Invasive meningococcal disease</t>
         </is>
       </c>
       <c r="Y240" t="inlineStr">
@@ -45813,12 +45913,12 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
@@ -45828,7 +45928,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:PL:national</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -45863,17 +45963,17 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -45896,7 +45996,7 @@
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_PL_ECDC_MENI_ANNUAL</t>
         </is>
       </c>
       <c r="AT240" t="n">
@@ -45909,42 +46009,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -46006,19 +46106,19 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O241" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -46162,19 +46262,19 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O242" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
@@ -46396,19 +46496,19 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
         <v>0</v>
@@ -46541,19 +46641,19 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O244" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -46697,19 +46797,19 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O245" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -46931,19 +47031,19 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O246" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -47087,19 +47187,19 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O247" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
@@ -47321,19 +47421,19 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
         <v>0</v>
@@ -47466,19 +47566,19 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N249" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O249" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -47622,19 +47722,19 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N250" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O250" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
@@ -47856,19 +47956,19 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O251" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -48012,19 +48112,19 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N252" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O252" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
@@ -48246,19 +48346,19 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q253" t="n">
         <v>0</v>
@@ -48391,19 +48491,19 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N254" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O254" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -48547,19 +48647,19 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -48781,19 +48881,19 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O256" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -48937,19 +49037,19 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O257" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -49171,19 +49271,19 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q258" t="n">
         <v>0</v>
@@ -49316,19 +49416,19 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N259" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O259" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -49472,19 +49572,19 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N260" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O260" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U260" t="inlineStr">
         <is>
@@ -49706,19 +49806,19 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N261" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O261" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -49862,19 +49962,19 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N262" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O262" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -50096,12 +50196,12 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N263" t="n">
@@ -50241,19 +50341,19 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N264" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O264" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -50397,19 +50497,19 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N265" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O265" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -50631,19 +50731,19 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -50787,19 +50887,19 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -51021,12 +51121,12 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N268" t="n">
@@ -51166,19 +51266,19 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N269" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O269" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -51322,19 +51422,19 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N270" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O270" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
@@ -51556,19 +51656,19 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N271" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O271" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -51712,19 +51812,19 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N272" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O272" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
@@ -51946,12 +52046,12 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N273" t="n">
@@ -52091,19 +52191,19 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N274" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O274" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -52247,19 +52347,19 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
@@ -52481,19 +52581,19 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N276" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -52637,19 +52737,19 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N277" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O277" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -52871,12 +52971,12 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -53016,12 +53116,12 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -53172,12 +53272,12 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N280" t="n">
@@ -53406,12 +53506,12 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N281" t="n">
@@ -53562,12 +53662,12 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N282" t="n">
@@ -53796,12 +53896,12 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N283" t="n">
@@ -53941,19 +54041,19 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N284" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O284" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -54097,19 +54197,19 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N285" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O285" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
@@ -54268,6 +54368,1856 @@
         </is>
       </c>
       <c r="BC285" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>5</v>
+      </c>
+      <c r="O286" t="n">
+        <v>5</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>5</v>
+      </c>
+      <c r="O287" t="n">
+        <v>5</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN287" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr"/>
+      <c r="AT288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>8</v>
+      </c>
+      <c r="O289" t="n">
+        <v>8</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>8</v>
+      </c>
+      <c r="O290" t="n">
+        <v>8</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM290" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN290" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" t="n">
+        <v>2</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="n">
+        <v>2</v>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ292" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK292" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM292" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN292" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>8</v>
+      </c>
+      <c r="O294" t="n">
+        <v>8</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>8</v>
+      </c>
+      <c r="O295" t="n">
+        <v>8</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN295" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -54389,7 +56339,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -54399,7 +56349,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11">
@@ -54419,7 +56369,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -54429,7 +56379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -54451,7 +56401,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1372</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="16">
